--- a/Project/outputs/tables/table_lstm_metrics_h1.xlsx
+++ b/Project/outputs/tables/table_lstm_metrics_h1.xlsx
@@ -482,19 +482,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0005535745876841247</v>
+        <v>0.0004888336989097297</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0115821585059166</v>
+        <v>0.01184635516256094</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02352816583765349</v>
+        <v>0.02210958387011682</v>
       </c>
       <c r="E2" t="n">
-        <v>6.843154907226562</v>
+        <v>7.677414417266846</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5281954887218046</v>
+        <v>0.541970802919708</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -513,23 +513,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0003509967646095902</v>
+        <v>0.0004508752026595175</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009707726538181305</v>
+        <v>0.01200407277792692</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01873490764881402</v>
+        <v>0.02123382213967889</v>
       </c>
       <c r="E3" t="n">
-        <v>6.388571262359619</v>
+        <v>7.275474071502686</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5300751879699248</v>
+        <v>0.5456204379562044</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -548,23 +548,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0003620331990532577</v>
+        <v>0.0004885040107183158</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01085708849132061</v>
+        <v>0.01247019786387682</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01902717002218821</v>
+        <v>0.02210212683698824</v>
       </c>
       <c r="E4" t="n">
-        <v>6.129380226135254</v>
+        <v>7.803284168243408</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5456204379562044</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -583,23 +583,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0004398312303237617</v>
+        <v>0.0003280531673226506</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01062080636620522</v>
+        <v>0.01097457110881805</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02097215368825438</v>
+        <v>0.01811223805394161</v>
       </c>
       <c r="E5" t="n">
-        <v>5.816079139709473</v>
+        <v>6.456085205078125</v>
       </c>
       <c r="F5" t="n">
-        <v>0.543233082706767</v>
+        <v>0.5857664233576643</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000265853654127568</v>
+        <v>0.0002431421598885208</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009368102066218853</v>
+        <v>0.009923168458044529</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0163050192924623</v>
+        <v>0.01559301638197436</v>
       </c>
       <c r="E6" t="n">
-        <v>4.754648208618164</v>
+        <v>5.392972469329834</v>
       </c>
       <c r="F6" t="n">
-        <v>0.556390977443609</v>
+        <v>0.541970802919708</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -653,23 +653,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0002761162759270519</v>
+        <v>0.0002881507098209113</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01014415640383959</v>
+        <v>0.009840032085776329</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01661674685150652</v>
+        <v>0.01697500249840663</v>
       </c>
       <c r="E7" t="n">
-        <v>5.157536506652832</v>
+        <v>5.647013664245605</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5150375939849624</v>
+        <v>0.5346715328467153</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -688,23 +688,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0004320803273003548</v>
+        <v>0.0005005246493965387</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01294710766524076</v>
+        <v>0.01248555816709995</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02078654197552721</v>
+        <v>0.02237240821629488</v>
       </c>
       <c r="E8" t="n">
-        <v>6.419454574584961</v>
+        <v>5.911120891571045</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5244360902255639</v>
+        <v>0.541970802919708</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0002320477360626683</v>
+        <v>0.0002335125464014709</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008748695254325867</v>
+        <v>0.009756595827639103</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01523311314415633</v>
+        <v>0.01528111731521851</v>
       </c>
       <c r="E9" t="n">
-        <v>4.947704315185547</v>
+        <v>6.573817729949951</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4906015037593985</v>
+        <v>0.4854014598540146</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0003640667218860472</v>
+        <v>0.0003776995181397069</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0104969801614061</v>
+        <v>0.01116256893146783</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01890047730757031</v>
+        <v>0.01922241441407749</v>
       </c>
       <c r="E10" t="n">
-        <v>5.807065963745117</v>
+        <v>6.592147827148438</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5324248120300752</v>
+        <v>0.5403740875912408</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0002120547869708389</v>
+        <v>0.0002116172690875828</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00842426810413599</v>
+        <v>0.009300312027335167</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01456210104932797</v>
+        <v>0.01454707080781498</v>
       </c>
       <c r="E11" t="n">
-        <v>5.368874073028564</v>
+        <v>5.663061618804932</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5585106382978723</v>
+        <v>0.5372549019607843</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -828,23 +828,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.000115935763460584</v>
+        <v>0.0001992252218769863</v>
       </c>
       <c r="C12" t="n">
-        <v>0.006957431323826313</v>
+        <v>0.009734350256621838</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01076734709483185</v>
+        <v>0.01411471650005718</v>
       </c>
       <c r="E12" t="n">
-        <v>5.781048774719238</v>
+        <v>7.185055255889893</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5598404255319149</v>
+        <v>0.5424836601307189</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -863,23 +863,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0001380011235596612</v>
+        <v>0.0001390426477883011</v>
       </c>
       <c r="C13" t="n">
-        <v>0.008080233819782734</v>
+        <v>0.008330455049872398</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01174738794624836</v>
+        <v>0.01179163465293515</v>
       </c>
       <c r="E13" t="n">
-        <v>7.898635387420654</v>
+        <v>6.127520084381104</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5279255319148937</v>
+        <v>0.5228758169934641</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -898,23 +898,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0001647505559958518</v>
+        <v>0.0001723952445900068</v>
       </c>
       <c r="C14" t="n">
-        <v>0.00772940693423152</v>
+        <v>0.009800834581255913</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01283551931149853</v>
+        <v>0.01312993696062577</v>
       </c>
       <c r="E14" t="n">
-        <v>5.613956451416016</v>
+        <v>10.2240104675293</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5478723404255319</v>
+        <v>0.530718954248366</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0003978993918281049</v>
+        <v>0.0004391600959934294</v>
       </c>
       <c r="C15" t="n">
-        <v>0.008946005254983902</v>
+        <v>0.01017350889742374</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01994741566790307</v>
+        <v>0.02095614697394131</v>
       </c>
       <c r="E15" t="n">
-        <v>4.483746528625488</v>
+        <v>4.961443901062012</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5731382978723404</v>
+        <v>0.534640522875817</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -968,23 +968,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0005518231773748994</v>
+        <v>0.0002826576819643378</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0113879619166255</v>
+        <v>0.009077160619199276</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02349091691217904</v>
+        <v>0.01681242641513526</v>
       </c>
       <c r="E16" t="n">
-        <v>4.811178207397461</v>
+        <v>5.499865055084229</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5452127659574468</v>
+        <v>0.5398692810457516</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1003,23 +1003,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.0002656458527781069</v>
+        <v>0.0005858136573806405</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01162777189165354</v>
+        <v>0.01286925934255123</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01629864573448073</v>
+        <v>0.02420358769646848</v>
       </c>
       <c r="E17" t="n">
-        <v>7.434823989868164</v>
+        <v>5.474303722381592</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4773936170212766</v>
+        <v>0.5464052287581699</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1038,23 +1038,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0002515322412364185</v>
+        <v>0.0003014383546542376</v>
       </c>
       <c r="C18" t="n">
-        <v>0.008702288381755352</v>
+        <v>0.01023626420646906</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01585976800701758</v>
+        <v>0.01736198014784712</v>
       </c>
       <c r="E18" t="n">
-        <v>6.224672794342041</v>
+        <v>8.083950042724609</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4853723404255319</v>
+        <v>0.4784313725490196</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0002622053616505582</v>
+        <v>0.0002914187716669403</v>
       </c>
       <c r="C19" t="n">
-        <v>0.008981920953374356</v>
+        <v>0.009940268122591078</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01568863771543589</v>
+        <v>0.01661468751935316</v>
       </c>
       <c r="E19" t="n">
-        <v>5.952116966247559</v>
+        <v>6.652400970458984</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5344082446808511</v>
+        <v>0.5290849673202613</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
